--- a/artfynd/A 47997-2023 artfynd.xlsx
+++ b/artfynd/A 47997-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123710585</v>
       </c>
       <c r="B2" t="n">
-        <v>58313</v>
+        <v>58319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Blomqvist, Julius Wengelin Grantén, Inge Karlqvist</t>
+          <t>Fredrik Blomqvist, Julius Wengelin Grantén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 47997-2023 artfynd.xlsx
+++ b/artfynd/A 47997-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123710585</v>
       </c>
       <c r="B2" t="n">
-        <v>58319</v>
+        <v>58322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47997-2023 artfynd.xlsx
+++ b/artfynd/A 47997-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123710585</v>
       </c>
       <c r="B2" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
